--- a/output/pdf_financials_xlsx/EMP.A.xlsx
+++ b/output/pdf_financials_xlsx/EMP.A.xlsx
@@ -2529,7 +2529,7 @@
         <v>1008.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>890.5</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>812.3</v>
@@ -2651,7 +2651,7 @@
         <v>1008.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>890.5</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>812.3</v>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
+          <t>CashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">

--- a/output/pdf_financials_xlsx/EMP.A.xlsx
+++ b/output/pdf_financials_xlsx/EMP.A.xlsx
@@ -2529,7 +2529,7 @@
         <v>1008.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>890.5</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>812.3</v>
@@ -2651,7 +2651,7 @@
         <v>1008.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>890.5</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>812.3</v>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">

--- a/output/pdf_financials_xlsx/EMP.A.xlsx
+++ b/output/pdf_financials_xlsx/EMP.A.xlsx
@@ -7391,13 +7391,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>137.1</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>176.7</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -60034,7 +60034,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -62786,7 +62790,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E525" s="5" t="n">
         <v>78</v>
       </c>

--- a/output/pdf_financials_xlsx/EMP.A.xlsx
+++ b/output/pdf_financials_xlsx/EMP.A.xlsx
@@ -7976,22 +7976,22 @@
         <v>0</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-153.6</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-248.9</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-350</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="S121" s="3" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="122">
@@ -40500,7 +40500,11 @@
           <t>Repurchase of common shares 19</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -42582,7 +42586,11 @@
           <t>Repurchase of common shares 18</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -43788,7 +43796,11 @@
           <t>Repurchase of common shares (Note 18)</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -46916,7 +46928,11 @@
           <t>Repurchase of common shares (Note 19)</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -71714,7 +71730,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
